--- a/loss-time/outputs/Nhap_lieu_05-10_den_26-10.xlsx
+++ b/loss-time/outputs/Nhap_lieu_05-10_den_26-10.xlsx
@@ -17255,7 +17255,7 @@
         <v>0.3125</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>2</v>
@@ -17287,7 +17287,7 @@
         <v>0.3125</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4</v>
@@ -17323,7 +17323,7 @@
         <v>0.3125</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>1</v>
@@ -17359,7 +17359,7 @@
         <v>0.3125</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>1</v>
@@ -17395,7 +17395,7 @@
         <v>0.3125</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1</v>
@@ -17431,7 +17431,7 @@
         <v>0.3125</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>1</v>
@@ -17467,7 +17467,7 @@
         <v>0.3125</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1</v>
@@ -17503,7 +17503,7 @@
         <v>0.3125</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>1</v>
@@ -17539,7 +17539,7 @@
         <v>0.3125</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         <v>0.3125</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1</v>
@@ -17611,7 +17611,7 @@
         <v>0.3125</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1</v>
@@ -17647,7 +17647,7 @@
         <v>0.3125</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>1</v>
@@ -17683,7 +17683,7 @@
         <v>0.3125</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>1</v>
@@ -17719,7 +17719,7 @@
         <v>0.3125</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>1</v>
@@ -17755,7 +17755,7 @@
         <v>0.3125</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>1</v>
@@ -17791,7 +17791,7 @@
         <v>0.3125</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>1</v>

--- a/loss-time/outputs/Nhap_lieu_05-10_den_26-10.xlsx
+++ b/loss-time/outputs/Nhap_lieu_05-10_den_26-10.xlsx
@@ -17255,7 +17255,7 @@
         <v>0.3125</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>2</v>
@@ -17287,7 +17287,7 @@
         <v>0.3125</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4</v>
@@ -17323,7 +17323,7 @@
         <v>0.3125</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>1</v>
@@ -17359,7 +17359,7 @@
         <v>0.3125</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>1</v>
@@ -17395,7 +17395,7 @@
         <v>0.3125</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1</v>
@@ -17431,7 +17431,7 @@
         <v>0.3125</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>1</v>
@@ -17467,7 +17467,7 @@
         <v>0.3125</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1</v>
@@ -17503,7 +17503,7 @@
         <v>0.3125</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>1</v>
@@ -17539,7 +17539,7 @@
         <v>0.3125</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         <v>0.3125</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1</v>
@@ -17611,7 +17611,7 @@
         <v>0.3125</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1</v>
@@ -17647,7 +17647,7 @@
         <v>0.3125</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>1</v>
@@ -17683,7 +17683,7 @@
         <v>0.3125</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>1</v>
@@ -17719,7 +17719,7 @@
         <v>0.3125</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>1</v>
@@ -17755,7 +17755,7 @@
         <v>0.3125</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>1</v>
@@ -17791,7 +17791,7 @@
         <v>0.3125</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>1</v>
